--- a/output/pdf_financials_xlsx/COV.xlsx
+++ b/output/pdf_financials_xlsx/COV.xlsx
@@ -6367,31 +6367,31 @@
         <v>0</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.452435</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.076114</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.372612</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.5657720000000001</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>1.106246</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>3.013209</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>2.951395</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>3.130413</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>3.97675</v>
       </c>
     </row>
     <row r="92">
@@ -12188,7 +12188,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -17690,7 +17694,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -20024,7 +20032,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COV.xlsx
+++ b/output/pdf_financials_xlsx/COV.xlsx
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.62626</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.192999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.053314</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.052697</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2314,16 +2314,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.740847</v>
+        <v>-4.367107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.874809</v>
+        <v>-4.68181</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.934947</v>
+        <v>-3.881633</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.561941</v>
+        <v>-3.509244</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.991382</v>
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.740847</v>
+        <v>-4.367107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.480765</v>
+        <v>-4.287766</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.489188</v>
+        <v>-3.435874</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.201523</v>
+        <v>-3.148826</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.991382</v>
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-151.2689154533522</v>
+        <v>-176.5930388381943</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-214.1318674176569</v>
+        <v>-204.9086128439981</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-107.9887232298185</v>
+        <v>-106.3386800707011</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-123.7052578703838</v>
+        <v>-121.6690719757344</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-105.2177028252111</v>
@@ -44358,7 +44358,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -45202,7 +45202,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" s="5" t="n">

--- a/output/pdf_financials_xlsx/COV.xlsx
+++ b/output/pdf_financials_xlsx/COV.xlsx
@@ -2409,7 +2409,7 @@
         <v>0.360418</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.352295</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.148464</v>
+        <v>0.356395</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.224142</v>
+        <v>0.629888</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>-3.148826</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.991382</v>
+        <v>-3.639087</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>-121.6690719757344</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-105.2177028252111</v>
+        <v>-95.93077648821614</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.360418</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.352295</v>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.356395</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.629888</v>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
@@ -26732,7 +26732,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -26838,7 +26842,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29816,7 +29820,11 @@
           <t>Depreciation - property, plant and equipment</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -29920,7 +29928,11 @@
           <t>Amortization - intangible assets</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
